--- a/desafios/def013 - 01/Novo(a) Microsoft Excel Worksheet.xlsx
+++ b/desafios/def013 - 01/Novo(a) Microsoft Excel Worksheet.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
     <sheet name="Plan2" sheetId="2" r:id="rId2"/>
+    <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>A</t>
   </si>
@@ -57,6 +58,93 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Nomes</t>
+  </si>
+  <si>
+    <t>Filmes</t>
+  </si>
+  <si>
+    <t>Mulheres</t>
+  </si>
+  <si>
+    <t>Homens</t>
+  </si>
+  <si>
+    <t>Ana Maria Sanros</t>
+  </si>
+  <si>
+    <t>Beatris Souza</t>
+  </si>
+  <si>
+    <t>Cláudia Melo</t>
+  </si>
+  <si>
+    <t>Bruno Mendonça</t>
+  </si>
+  <si>
+    <t>Daniel Lourenço</t>
+  </si>
+  <si>
+    <t>Fabiano Mota</t>
+  </si>
+  <si>
+    <t>Alien</t>
+  </si>
+  <si>
+    <t>Rambo</t>
+  </si>
+  <si>
+    <t>Vingadores</t>
+  </si>
+  <si>
+    <t>Hulk</t>
+  </si>
+  <si>
+    <t>Inception</t>
+  </si>
+  <si>
+    <t>Batman</t>
+  </si>
+  <si>
+    <t>Oblivion</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>Big Hero</t>
+  </si>
+  <si>
+    <t>Intocáveis</t>
+  </si>
+  <si>
+    <t>Amnésia</t>
+  </si>
+  <si>
+    <t>Gladiador</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Oldboy</t>
+  </si>
+  <si>
+    <t>Dangal</t>
+  </si>
+  <si>
+    <t>Star Wars 5</t>
+  </si>
+  <si>
+    <t>Taxi Driver</t>
+  </si>
+  <si>
+    <t>Toy Story</t>
   </si>
 </sst>
 </file>
@@ -107,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -117,6 +205,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,7 +529,7 @@
       <c r="B1" s="2">
         <v>2</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="4">
         <v>3</v>
       </c>
       <c r="D1" s="2">
@@ -449,35 +543,35 @@
       <c r="B2" s="2">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>8</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>11</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2">
         <v>13</v>
       </c>
@@ -508,18 +602,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -531,10 +625,10 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -544,10 +638,10 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
@@ -557,16 +651,16 @@
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
@@ -582,4 +676,134 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/desafios/def013 - 01/Novo(a) Microsoft Excel Worksheet.xlsx
+++ b/desafios/def013 - 01/Novo(a) Microsoft Excel Worksheet.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
     <sheet name="Plan2" sheetId="2" r:id="rId2"/>
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
+    <sheet name="Plan4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
   <si>
     <t>A</t>
   </si>
@@ -145,13 +146,43 @@
   </si>
   <si>
     <t>Toy Story</t>
+  </si>
+  <si>
+    <t>Área</t>
+  </si>
+  <si>
+    <t>Disciplina</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Exatas</t>
+  </si>
+  <si>
+    <t>Média Exátas</t>
+  </si>
+  <si>
+    <t>Nota 1</t>
+  </si>
+  <si>
+    <t>Nota 2</t>
+  </si>
+  <si>
+    <t>Humanas</t>
+  </si>
+  <si>
+    <t>Média Humanas</t>
+  </si>
+  <si>
+    <t>0.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,16 +190,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -191,11 +236,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -211,6 +308,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,7 +659,7 @@
       <c r="B1" s="2">
         <v>2</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1" s="6">
         <v>3</v>
       </c>
       <c r="D1" s="2">
@@ -543,35 +673,35 @@
       <c r="B2" s="2">
         <v>6</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="6"/>
       <c r="D2" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="6">
         <v>8</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>10</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <v>11</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="2">
         <v>13</v>
       </c>
@@ -602,18 +732,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -625,10 +755,10 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -638,10 +768,10 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
@@ -651,16 +781,16 @@
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
@@ -698,14 +828,14 @@
       <c r="B1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -722,7 +852,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
@@ -737,7 +867,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="6"/>
       <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
@@ -752,7 +882,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -769,7 +899,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
@@ -784,7 +914,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
@@ -806,4 +936,174 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>